--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C22838C-CF3A-EB4A-B204-99D11289CA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430D9CC-1F64-4ECA-A57E-33978707DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1440,16 +1438,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1466,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1477,13 +1475,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>3458</v>
+        <v>3514</v>
       </c>
       <c r="E2" s="5">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24.57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1500,7 +1498,7 @@
         <v>52.45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1511,13 +1509,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="E4" s="5">
-        <v>89.93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1528,13 +1526,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="E5" s="5">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>115.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1545,13 +1543,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>807</v>
+        <v>823</v>
       </c>
       <c r="E6" s="5">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>92.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1562,13 +1560,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1881</v>
+        <v>1951</v>
       </c>
       <c r="E7" s="5">
-        <v>22.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1579,13 +1577,13 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>2441</v>
+        <v>2491</v>
       </c>
       <c r="E8" s="5">
-        <v>29.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1596,13 +1594,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2643</v>
+        <v>2693</v>
       </c>
       <c r="E9" s="5">
-        <v>28.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1613,13 +1611,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="E10" s="5">
-        <v>55.14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54.93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1630,13 +1628,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E11" s="5">
-        <v>152.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>152.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1647,13 +1645,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>729</v>
+        <v>745</v>
       </c>
       <c r="E12" s="5">
-        <v>88.76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88.89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1664,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1920</v>
+        <v>1966</v>
       </c>
       <c r="E13" s="5">
-        <v>36.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1681,13 +1679,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E14" s="5">
-        <v>144.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>144.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1704,7 +1702,7 @@
         <v>55.06</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1715,13 +1713,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>5463</v>
+        <v>5587</v>
       </c>
       <c r="E16" s="5">
-        <v>11.46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1732,13 +1730,13 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>3325</v>
+        <v>3391</v>
       </c>
       <c r="E17" s="5">
-        <v>21.19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1749,13 +1747,13 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>3034</v>
+        <v>3084</v>
       </c>
       <c r="E18" s="5">
-        <v>29.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29.28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1766,13 +1764,13 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="E19" s="5">
-        <v>86.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87.26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1783,13 +1781,13 @@
         <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E20" s="5">
-        <v>194.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>196.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1800,13 +1798,13 @@
         <v>43</v>
       </c>
       <c r="D21" s="5">
-        <v>2510</v>
+        <v>2580</v>
       </c>
       <c r="E21" s="5">
-        <v>22.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22.57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1817,13 +1815,13 @@
         <v>45</v>
       </c>
       <c r="D22" s="5">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="E22" s="5">
-        <v>85.33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1834,13 +1832,13 @@
         <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>3148</v>
+        <v>3238</v>
       </c>
       <c r="E23" s="5">
-        <v>16.420000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1851,13 +1849,13 @@
         <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E24" s="5">
-        <v>265.86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>265.97000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1868,13 +1866,13 @@
         <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>5078</v>
+        <v>5224</v>
       </c>
       <c r="E25" s="5">
         <v>11.07</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1885,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="E26" s="5">
-        <v>72.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>72.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1902,13 +1900,13 @@
         <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>3052</v>
+        <v>3108</v>
       </c>
       <c r="E27" s="5">
-        <v>26.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26.29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1925,7 +1923,7 @@
         <v>878.52</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1936,13 +1934,13 @@
         <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="E29" s="5">
-        <v>86.18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>86.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1953,13 +1951,13 @@
         <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>1681</v>
+        <v>1827</v>
       </c>
       <c r="E30" s="5">
-        <v>11.43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1970,13 +1968,13 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>698</v>
+        <v>752</v>
       </c>
       <c r="E31" s="5">
-        <v>29.45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1987,13 +1985,13 @@
         <v>64</v>
       </c>
       <c r="D32" s="5">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E32" s="5">
-        <v>116.56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116.85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2004,10 +2002,10 @@
         <v>65</v>
       </c>
       <c r="D33" s="5">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E33" s="5">
-        <v>172.77</v>
+        <v>174.32</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,37 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430D9CC-1F64-4ECA-A57E-33978707DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Manthan" sheetId="1" r:id="rId1"/>
+    <sheet name="Manthan" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -156,6 +136,9 @@
     <t>MODEFENCE</t>
   </si>
   <si>
+    <t>Motilal Oswal NASDAQ 100 ETF</t>
+  </si>
+  <si>
     <t>MON100</t>
   </si>
   <si>
@@ -213,49 +196,58 @@
     <t>TNIDETF</t>
   </si>
   <si>
+    <t>Groww BSE Power ETF</t>
+  </si>
+  <si>
     <t>GROWWPOWER</t>
   </si>
   <si>
+    <t>Kotak Nifty Chemicals ETF</t>
+  </si>
+  <si>
     <t>CHEMICAL</t>
   </si>
   <si>
-    <t>Groww BSE Power ETF</t>
-  </si>
-  <si>
-    <t>Kotak Nifty Chemicals ETF</t>
+    <t>ICICI Prudential Gold ETF</t>
   </si>
   <si>
     <t>GOLDIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Silver ETF</t>
+  </si>
+  <si>
     <t>SILVERIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Gold ETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Silver ETF</t>
-  </si>
-  <si>
-    <t>Motilal Oswal NASDAQ 100 ETF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -263,12 +255,18 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -281,32 +279,47 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,85 +328,23 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -585,17 +536,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -613,19 +564,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -642,7 +593,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -667,7 +618,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -692,7 +643,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -717,7 +668,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -742,7 +693,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -767,7 +718,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -792,7 +743,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -817,7 +768,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -842,7 +793,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -855,32 +806,26 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -898,7 +843,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -923,7 +868,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -948,7 +893,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -973,7 +918,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -998,7 +943,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1023,7 +968,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1048,7 +993,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1073,7 +1018,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1098,7 +1043,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1123,7 +1068,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1136,15 +1081,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1158,7 +1097,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1176,19 +1115,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1205,7 +1144,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1230,7 +1169,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1255,7 +1194,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1280,7 +1219,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1305,7 +1244,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1330,7 +1269,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1355,7 +1294,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1380,7 +1319,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1405,7 +1344,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1418,77 +1357,69 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.85156" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.8516" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.6719" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s" s="4">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s" s="4">
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>3514</v>
+        <v>3600</v>
       </c>
       <c r="E2" s="5">
-        <v>24.57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s" s="4">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s" s="4">
         <v>8</v>
       </c>
       <c r="D3" s="5">
@@ -1498,423 +1429,423 @@
         <v>52.45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s" s="4">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s" s="4">
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>902</v>
+        <v>950</v>
       </c>
       <c r="E4" s="5">
-        <v>90.09</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>90.43000000000001</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s" s="4">
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="E5" s="5">
-        <v>115.05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>115.12</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s" s="4">
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>823</v>
+        <v>896</v>
       </c>
       <c r="E6" s="5">
-        <v>92.03</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92.06999999999999</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s" s="4">
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1951</v>
+        <v>2031</v>
       </c>
       <c r="E7" s="5">
-        <v>22.69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22.71</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s" s="4">
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>2491</v>
+        <v>2563</v>
       </c>
       <c r="E8" s="5">
-        <v>29.35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s" s="4">
         <v>19</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s" s="4">
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2693</v>
+        <v>2775</v>
       </c>
       <c r="E9" s="5">
-        <v>28.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28.56</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s" s="4">
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>782</v>
+        <v>836</v>
       </c>
       <c r="E10" s="5">
-        <v>54.93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54.54</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s" s="4">
         <v>23</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s" s="4">
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E11" s="5">
-        <v>152.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152.7</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s" s="4">
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="E12" s="5">
-        <v>88.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88.97</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s" s="4">
         <v>27</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s" s="4">
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1966</v>
+        <v>2036</v>
       </c>
       <c r="E13" s="5">
-        <v>36.43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s" s="4">
         <v>29</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s" s="4">
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="E14" s="5">
-        <v>144.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145.3</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s" s="4">
         <v>31</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s" s="4">
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>516</v>
+        <v>594</v>
       </c>
       <c r="E15" s="5">
-        <v>55.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60.69</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s" s="4">
         <v>33</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s" s="4">
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>5587</v>
+        <v>5941</v>
       </c>
       <c r="E16" s="5">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s" s="4">
         <v>35</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s" s="4">
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>3391</v>
+        <v>3469</v>
       </c>
       <c r="E17" s="5">
-        <v>21.24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21.29</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s" s="4">
         <v>37</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s" s="4">
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>3084</v>
+        <v>3165</v>
       </c>
       <c r="E18" s="5">
-        <v>29.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29.36</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s" s="4">
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>833</v>
+        <v>911</v>
       </c>
       <c r="E19" s="5">
-        <v>87.26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88.38</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" t="s" s="4">
         <v>41</v>
       </c>
+      <c r="C20" t="s" s="4">
+        <v>42</v>
+      </c>
       <c r="D20" s="5">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E20" s="5">
-        <v>196.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202.59</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" t="s" s="4">
         <v>43</v>
       </c>
+      <c r="C21" t="s" s="4">
+        <v>44</v>
+      </c>
       <c r="D21" s="5">
-        <v>2580</v>
+        <v>2660</v>
       </c>
       <c r="E21" s="5">
-        <v>22.57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22.59</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" t="s" s="4">
         <v>45</v>
       </c>
+      <c r="C22" t="s" s="4">
+        <v>46</v>
+      </c>
       <c r="D22" s="5">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="E22" s="5">
-        <v>85.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85.34999999999999</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" t="s" s="4">
         <v>47</v>
       </c>
+      <c r="C23" t="s" s="4">
+        <v>48</v>
+      </c>
       <c r="D23" s="5">
-        <v>3238</v>
+        <v>3348</v>
       </c>
       <c r="E23" s="5">
-        <v>16.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16.52</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="B24" t="s" s="4">
         <v>49</v>
       </c>
+      <c r="C24" t="s" s="4">
+        <v>50</v>
+      </c>
       <c r="D24" s="5">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E24" s="5">
-        <v>265.97000000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>265.93</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" t="s" s="4">
         <v>51</v>
       </c>
+      <c r="C25" t="s" s="4">
+        <v>52</v>
+      </c>
       <c r="D25" s="5">
-        <v>5224</v>
+        <v>5390</v>
       </c>
       <c r="E25" s="5">
         <v>11.07</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" t="s" s="4">
         <v>53</v>
       </c>
+      <c r="C26" t="s" s="4">
+        <v>54</v>
+      </c>
       <c r="D26" s="5">
-        <v>1156</v>
+        <v>1234</v>
       </c>
       <c r="E26" s="5">
-        <v>72.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73.05</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="B27" t="s" s="4">
         <v>55</v>
       </c>
+      <c r="C27" t="s" s="4">
+        <v>56</v>
+      </c>
       <c r="D27" s="5">
-        <v>3108</v>
+        <v>3272</v>
       </c>
       <c r="E27" s="5">
-        <v>26.29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="B28" t="s" s="4">
         <v>57</v>
+      </c>
+      <c r="C28" t="s" s="4">
+        <v>58</v>
       </c>
       <c r="D28" s="5">
         <v>48</v>
@@ -1923,94 +1854,94 @@
         <v>878.52</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="B29" t="s" s="4">
         <v>59</v>
       </c>
+      <c r="C29" t="s" s="4">
+        <v>60</v>
+      </c>
       <c r="D29" s="5">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="E29" s="5">
-        <v>86.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86.34999999999999</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s" s="4">
         <v>62</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="D30" s="5">
-        <v>1827</v>
+        <v>2105</v>
       </c>
       <c r="E30" s="5">
-        <v>11.42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" t="s" s="4">
         <v>63</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>61</v>
+      <c r="C31" t="s" s="4">
+        <v>64</v>
       </c>
       <c r="D31" s="5">
-        <v>752</v>
+        <v>857</v>
       </c>
       <c r="E31" s="5">
-        <v>29.49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29.44</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s" s="6">
         <v>66</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="D32" s="5">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="E32" s="5">
-        <v>116.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117.76</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" t="s" s="4">
         <v>67</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>65</v>
+      <c r="C33" t="s" s="6">
+        <v>68</v>
       </c>
       <c r="D33" s="5">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E33" s="5">
-        <v>174.32</v>
+        <v>175.76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -224,8 +224,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -298,7 +299,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -315,6 +316,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1406,10 +1410,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>3600</v>
+        <v>3693</v>
       </c>
       <c r="E2" s="5">
-        <v>24.66</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -1440,10 +1444,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>950</v>
+        <v>1001</v>
       </c>
       <c r="E4" s="5">
-        <v>90.43000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -1457,10 +1461,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>510</v>
-      </c>
-      <c r="E5" s="5">
-        <v>115.12</v>
+        <v>526</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1.151</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1474,10 +1478,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>896</v>
+        <v>972</v>
       </c>
       <c r="E6" s="5">
-        <v>92.06999999999999</v>
+        <v>92.02</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -1491,7 +1495,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>2031</v>
+        <v>2118</v>
       </c>
       <c r="E7" s="5">
         <v>22.71</v>
@@ -1508,10 +1512,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>2563</v>
+        <v>2640</v>
       </c>
       <c r="E8" s="5">
-        <v>29.42</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1525,10 +1529,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2775</v>
+        <v>2862</v>
       </c>
       <c r="E9" s="5">
-        <v>28.56</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1542,10 +1546,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>836</v>
+        <v>876</v>
       </c>
       <c r="E10" s="5">
-        <v>54.54</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1559,10 +1563,10 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E11" s="5">
-        <v>152.7</v>
+        <v>153.15</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1576,10 +1580,10 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="E12" s="5">
-        <v>88.97</v>
+        <v>89.01000000000001</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1593,10 +1597,10 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>2036</v>
+        <v>2112</v>
       </c>
       <c r="E13" s="5">
-        <v>36.3</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1610,10 +1614,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="E14" s="5">
-        <v>145.3</v>
+        <v>145.61</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1627,10 +1631,10 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>594</v>
+        <v>674</v>
       </c>
       <c r="E15" s="5">
-        <v>60.69</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1644,10 +1648,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>5941</v>
+        <v>6306</v>
       </c>
       <c r="E16" s="5">
-        <v>11.58</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1661,10 +1665,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>3469</v>
+        <v>3555</v>
       </c>
       <c r="E17" s="5">
-        <v>21.29</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1678,10 +1682,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>3165</v>
+        <v>3251</v>
       </c>
       <c r="E18" s="5">
-        <v>29.36</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1695,10 +1699,10 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>911</v>
+        <v>989</v>
       </c>
       <c r="E19" s="5">
-        <v>88.38</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1712,10 +1716,10 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="E20" s="5">
-        <v>202.59</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -1729,7 +1733,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>2660</v>
+        <v>2747</v>
       </c>
       <c r="E21" s="5">
         <v>22.59</v>
@@ -1746,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="E22" s="5">
-        <v>85.34999999999999</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1763,10 +1767,10 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>3348</v>
+        <v>3467</v>
       </c>
       <c r="E23" s="5">
-        <v>16.52</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1780,10 +1784,10 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E24" s="5">
-        <v>265.93</v>
+        <v>265.75</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1797,7 +1801,7 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>5390</v>
+        <v>5572</v>
       </c>
       <c r="E25" s="5">
         <v>11.07</v>
@@ -1814,10 +1818,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>1234</v>
+        <v>1315</v>
       </c>
       <c r="E26" s="5">
-        <v>73.05</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1831,10 +1835,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>3272</v>
+        <v>3443</v>
       </c>
       <c r="E27" s="5">
-        <v>26.36</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1865,10 +1869,10 @@
         <v>60</v>
       </c>
       <c r="D29" s="5">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="E29" s="5">
-        <v>86.34999999999999</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -1882,10 +1886,10 @@
         <v>62</v>
       </c>
       <c r="D30" s="5">
-        <v>2105</v>
+        <v>2399</v>
       </c>
       <c r="E30" s="5">
-        <v>11.37</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1899,10 +1903,10 @@
         <v>64</v>
       </c>
       <c r="D31" s="5">
-        <v>857</v>
+        <v>1076</v>
       </c>
       <c r="E31" s="5">
-        <v>29.44</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -1912,14 +1916,14 @@
       <c r="B32" t="s" s="4">
         <v>65</v>
       </c>
-      <c r="C32" t="s" s="6">
+      <c r="C32" t="s" s="7">
         <v>66</v>
       </c>
       <c r="D32" s="5">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="E32" s="5">
-        <v>117.76</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -1929,14 +1933,14 @@
       <c r="B33" t="s" s="4">
         <v>67</v>
       </c>
-      <c r="C33" t="s" s="6">
+      <c r="C33" t="s" s="7">
         <v>68</v>
       </c>
       <c r="D33" s="5">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E33" s="5">
-        <v>175.76</v>
+        <v>177.33</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -224,9 +224,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -299,7 +298,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -316,9 +315,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1463,8 +1459,8 @@
       <c r="D5" s="5">
         <v>526</v>
       </c>
-      <c r="E5" s="6">
-        <v>1.151</v>
+      <c r="E5" s="5">
+        <v>115.17</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1916,7 +1912,7 @@
       <c r="B32" t="s" s="4">
         <v>65</v>
       </c>
-      <c r="C32" t="s" s="7">
+      <c r="C32" t="s" s="6">
         <v>66</v>
       </c>
       <c r="D32" s="5">
@@ -1933,7 +1929,7 @@
       <c r="B33" t="s" s="4">
         <v>67</v>
       </c>
-      <c r="C33" t="s" s="7">
+      <c r="C33" t="s" s="6">
         <v>68</v>
       </c>
       <c r="D33" s="5">
